--- a/sample_templates/浆粕流水.xlsx
+++ b/sample_templates/浆粕流水.xlsx
@@ -529,13 +529,11 @@
           <t>原材料</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>原料仓</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>5000</v>
       </c>
@@ -544,8 +542,6 @@
           <t>千克</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>领料出库</t>
@@ -583,13 +579,11 @@
           <t>原材料</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>原料仓</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>20000</v>
       </c>
@@ -598,8 +592,6 @@
           <t>千克</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>领料出库</t>
@@ -637,13 +629,11 @@
           <t>产成品</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>成品仓</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>3000</v>
       </c>
@@ -652,8 +642,6 @@
           <t>千克</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>生产入库</t>
@@ -691,13 +679,11 @@
           <t>产成品</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>成品仓</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>800</v>
       </c>
@@ -706,8 +692,6 @@
           <t>千克</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>销售出库</t>
@@ -727,7 +711,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>（示例行自动跳过；领料出库行=原料计入材料成本，生产入库/销售出库行=成品；金额可不填按历史单价）</t>
+          <t>（示例行自动跳过；领料出库行=原料计入材料成本，备注须注明用途（如 用于21.03芳纶浆粕 / 用于芳纶浆粕/微纤）；生产入库/销售出库行=成品；金额可不填按历史单价）</t>
         </is>
       </c>
     </row>

--- a/sample_templates/浆粕流水.xlsx
+++ b/sample_templates/浆粕流水.xlsx
@@ -711,7 +711,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>（示例行自动跳过；领料出库行=原料计入材料成本，备注须注明用途（如 用于21.03芳纶浆粕 / 用于芳纶浆粕/微纤）；生产入库/销售出库行=成品；金额可不填按历史单价）</t>
+          <t>（示例行自动跳过；领料出库行=原料计入材料成本，备注建议注明用途（如 用于21.03芳纶浆粕 / 用于芳纶浆粕/微纤），未注明时按物料名称自动分类；生产入库/销售出库行=成品；金额可不填按历史单价）</t>
         </is>
       </c>
     </row>
